--- a/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
+++ b/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
@@ -328,12 +328,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/22 16:15:32</t>
+          <t>09/30 19:21:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -343,7 +343,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -355,12 +355,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/09 11:40:10</t>
+          <t>07/22 16:15:32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -370,7 +370,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -382,12 +382,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/09 09:55:21</t>
+          <t>07/09 11:40:10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -397,7 +397,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -409,12 +409,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/07 14:00:58</t>
+          <t>07/09 09:55:21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -424,7 +424,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -436,83 +436,110 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>07/07 14:00:58</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>07/07 12:04:55</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>313000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>37466.01</t>
+          <t>313000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21245</t>
+          <t>37466.01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>22245</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>16221.01</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>15221.01</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
+++ b/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
@@ -328,12 +328,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/30 19:21:28</t>
+          <t>09/30 19:30:31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -355,12 +355,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/22 16:15:32</t>
+          <t>09/30 19:21:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -370,7 +370,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -382,12 +382,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/09 11:40:10</t>
+          <t>07/22 16:15:32</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -397,7 +397,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -409,12 +409,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/09 09:55:21</t>
+          <t>07/09 11:40:10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -424,7 +424,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -436,12 +436,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/07 14:00:58</t>
+          <t>07/09 09:55:21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -463,83 +463,110 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>07/07 14:00:58</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>07/07 12:04:55</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>313000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>37466.01</t>
+          <t>313000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22245</t>
+          <t>37466.01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>37464</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>15221.01</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2.01</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
+++ b/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 18:35:24</t>
+          <t>10/09 11:01:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>120000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16219.51</t>
+          <t>14285.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/22 14:50:57</t>
+          <t>09/30 18:35:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>16219.51</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>陈琦兰</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/09 09:55:07</t>
+          <t>07/22 14:50:57</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>陈琦兰</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,166 +201,181 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07/09 09:55:07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5952.38</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>07/07 12:04:51</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>5882.35</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/30 19:30:31</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/30 19:21:28</t>
+          <t>10/09 11:01:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -370,7 +385,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -382,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/22 16:15:32</t>
+          <t>09/30 19:30:31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -397,7 +412,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -409,12 +424,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/09 11:40:10</t>
+          <t>09/30 19:21:28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -436,12 +451,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/09 09:55:21</t>
+          <t>07/22 16:15:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -463,12 +478,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/07 14:00:58</t>
+          <t>07/09 11:40:10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -490,12 +505,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/07 12:04:55</t>
+          <t>07/09 09:55:21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -514,59 +529,113 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>07/07 14:00:58</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>313000</t>
-        </is>
-      </c>
-    </row>
+          <t>07/07 12:04:55</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>37466.01</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>37464</t>
+          <t>433000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>51751.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>37652</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2.01</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14099.73</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
+++ b/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
@@ -370,12 +370,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/09 11:01:56</t>
+          <t>10/09 12:31:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -397,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/30 19:30:31</t>
+          <t>10/09 11:01:56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -412,7 +412,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -424,12 +424,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/30 19:21:28</t>
+          <t>09/30 19:30:31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -451,12 +451,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/22 16:15:32</t>
+          <t>09/30 19:21:28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -478,12 +478,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/09 11:40:10</t>
+          <t>07/22 16:15:32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -505,12 +505,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/09 09:55:21</t>
+          <t>07/09 11:40:10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -532,12 +532,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/07 14:00:58</t>
+          <t>07/09 09:55:21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -559,83 +559,110 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>07/07 14:00:58</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>07/07 12:04:55</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>433000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>51751.73</t>
+          <t>433000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>37652</t>
+          <t>51751.73</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>14099.73</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2.73</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
+++ b/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/09 11:01:53</t>
+          <t>10/12 14:15:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>120000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14285.71</t>
+          <t>6024.1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/30 18:35:24</t>
+          <t>10/09 11:01:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>120000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16219.51</t>
+          <t>14285.71</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/22 14:50:57</t>
+          <t>09/30 18:35:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>16219.51</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>陈琦兰</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/09 09:55:07</t>
+          <t>07/22 14:50:57</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>陈琦兰</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,166 +243,181 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07/09 09:55:07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5952.38</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>07/07 12:04:51</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>5882.35</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/09 12:31:53</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/09 11:01:56</t>
+          <t>10/12 16:14:28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/30 19:30:31</t>
+          <t>10/09 12:31:53</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -439,7 +454,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -451,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/30 19:21:28</t>
+          <t>10/09 11:01:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -466,7 +481,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -478,12 +493,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/22 16:15:32</t>
+          <t>09/30 19:30:31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -493,7 +508,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -505,12 +520,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/09 11:40:10</t>
+          <t>09/30 19:21:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -532,12 +547,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/09 09:55:21</t>
+          <t>07/22 16:15:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -559,12 +574,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/07 14:00:58</t>
+          <t>07/09 11:40:10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -586,12 +601,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/07 12:04:55</t>
+          <t>07/09 09:55:21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -610,59 +625,113 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>07/07 14:00:58</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>433000</t>
-        </is>
-      </c>
-    </row>
+          <t>07/07 12:04:55</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>51751.73</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>483000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>57775.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>57773</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2.73</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2.82</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
+++ b/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/12 14:15:28</t>
+          <t>10/16 11:16:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>117000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6024.1</t>
+          <t>1376.47</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/09 11:01:53</t>
+          <t>10/12 14:15:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>120000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14285.71</t>
+          <t>6024.1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/30 18:35:24</t>
+          <t>10/09 11:01:53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>120000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16219.51</t>
+          <t>14285.71</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/22 14:50:57</t>
+          <t>09/30 18:35:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>16219.51</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>陈琦兰</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/09 09:55:07</t>
+          <t>07/22 14:50:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>陈琦兰</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,166 +285,181 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>07/09 09:55:07</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5952.38</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>07/07 12:04:51</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>5882.35</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/12 16:14:28</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10/09 12:31:53</t>
+          <t>10/12 16:14:28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10/09 11:01:56</t>
+          <t>10/09 12:31:53</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -493,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/30 19:30:31</t>
+          <t>10/09 11:01:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -508,7 +523,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -520,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/30 19:21:28</t>
+          <t>09/30 19:30:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -547,12 +562,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/22 16:15:32</t>
+          <t>09/30 19:21:28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -562,7 +577,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -574,12 +589,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/09 11:40:10</t>
+          <t>07/22 16:15:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -589,7 +604,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -601,12 +616,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/09 09:55:21</t>
+          <t>07/09 11:40:10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -616,7 +631,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -628,12 +643,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/07 14:00:58</t>
+          <t>07/09 09:55:21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -643,7 +658,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -655,83 +670,110 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>07/07 14:00:58</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>07/07 12:04:55</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>483000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>57775.82</t>
+          <t>600000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>57773</t>
+          <t>59152.29</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>57773</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2.82</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1379.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
+++ b/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/16 11:16:59</t>
+          <t>10/16 11:23:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1376.47</t>
+          <t>13764.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/12 14:15:28</t>
+          <t>10/16 11:16:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>117000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6024.1</t>
+          <t>1376.47</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/09 11:01:53</t>
+          <t>10/12 14:15:28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>120000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14285.71</t>
+          <t>6024.1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/30 18:35:24</t>
+          <t>10/09 11:01:53</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>120000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16219.51</t>
+          <t>14285.71</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/22 14:50:57</t>
+          <t>09/30 18:35:24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>16219.51</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>陈琦兰</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/09 09:55:07</t>
+          <t>07/22 14:50:57</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,17 +300,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t/>
+          <t>陈琦兰</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,166 +327,181 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>07/09 09:55:07</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>5952.38</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>07/07 12:04:51</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>5882.35</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10/12 16:14:28</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10/09 12:31:53</t>
+          <t>10/12 16:14:28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10/09 11:01:56</t>
+          <t>10/09 12:31:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/30 19:30:31</t>
+          <t>10/09 11:01:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -550,7 +565,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -562,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/30 19:21:28</t>
+          <t>09/30 19:30:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -589,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/22 16:15:32</t>
+          <t>09/30 19:21:28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -604,7 +619,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -616,12 +631,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/09 11:40:10</t>
+          <t>07/22 16:15:32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -631,7 +646,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -643,12 +658,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/09 09:55:21</t>
+          <t>07/09 11:40:10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -658,7 +673,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -670,12 +685,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/07 14:00:58</t>
+          <t>07/09 09:55:21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -685,7 +700,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -697,83 +712,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>07/07 14:00:58</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>07/07 12:04:55</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>600000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>59152.29</t>
+          <t>717000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>57773</t>
+          <t>72917</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>57773</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1379.29</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>15144</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
+++ b/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
@@ -496,12 +496,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10/12 16:14:28</t>
+          <t>10/16 13:58:38</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -523,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10/09 12:31:53</t>
+          <t>10/12 16:14:28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10/09 11:01:56</t>
+          <t>10/09 12:31:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/30 19:30:31</t>
+          <t>10/09 11:01:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -604,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/30 19:21:28</t>
+          <t>09/30 19:30:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -631,12 +631,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/22 16:15:32</t>
+          <t>09/30 19:21:28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -658,12 +658,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/09 11:40:10</t>
+          <t>07/22 16:15:32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -685,12 +685,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/09 09:55:21</t>
+          <t>07/09 11:40:10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -712,12 +712,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/07 14:00:58</t>
+          <t>07/09 09:55:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -739,83 +739,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>07/07 14:00:58</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>07/07 12:04:55</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>717000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>72917</t>
+          <t>717000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>57773</t>
+          <t>72917</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>71537</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>15144</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1380</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
+++ b/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/16 11:23:28</t>
+          <t>10/29 10:37:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>117000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13764.71</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/16 11:16:59</t>
+          <t>10/16 11:23:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1376.47</t>
+          <t>13764.71</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/12 14:15:28</t>
+          <t>10/16 11:16:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>117000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6024.1</t>
+          <t>1376.47</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/09 11:01:53</t>
+          <t>10/12 14:15:28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>120000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14285.71</t>
+          <t>6024.1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/30 18:35:24</t>
+          <t>10/09 11:01:53</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>120000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16219.51</t>
+          <t>14285.71</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/22 14:50:57</t>
+          <t>09/30 18:35:24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,17 +300,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>16219.51</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>陈琦兰</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/09 09:55:07</t>
+          <t>07/22 14:50:57</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>陈琦兰</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,166 +369,181 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>07/09 09:55:07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>5952.38</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>07/07 12:04:51</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>5882.35</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10/16 13:58:38</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13764</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10/12 16:14:28</t>
+          <t>10/16 13:58:38</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10/09 12:31:53</t>
+          <t>10/12 16:14:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10/09 11:01:56</t>
+          <t>10/09 12:31:53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -604,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/30 19:30:31</t>
+          <t>10/09 11:01:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -619,7 +634,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -631,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/30 19:21:28</t>
+          <t>09/30 19:30:31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -658,12 +673,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/22 16:15:32</t>
+          <t>09/30 19:21:28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -673,7 +688,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -685,12 +700,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/09 11:40:10</t>
+          <t>07/22 16:15:32</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -700,7 +715,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -712,12 +727,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/09 09:55:21</t>
+          <t>07/09 11:40:10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -727,7 +742,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -739,12 +754,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/07 14:00:58</t>
+          <t>07/09 09:55:21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -754,7 +769,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -766,83 +781,110 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>07/07 14:00:58</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>07/07 12:04:55</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>717000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>72917</t>
+          <t>817000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>71537</t>
+          <t>84893.05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>71537</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1380</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>13356.05</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
+++ b/bills/JXZFSP01/-4969455652/3a0894aed0dc0c7a61de7633ebaff84a426fddeb8c685bb53a5392c1dd7bfe2c/bill-all.xlsx
@@ -538,12 +538,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10/16 13:58:38</t>
+          <t>10/29 15:26:59</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13764</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -565,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10/12 16:14:28</t>
+          <t>10/16 13:58:38</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -592,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10/09 12:31:53</t>
+          <t>10/12 16:14:28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -619,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10/09 11:01:56</t>
+          <t>10/09 12:31:53</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -646,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/30 19:30:31</t>
+          <t>10/09 11:01:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -673,12 +673,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/30 19:21:28</t>
+          <t>09/30 19:30:31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -700,12 +700,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/22 16:15:32</t>
+          <t>09/30 19:21:28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -727,12 +727,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/09 11:40:10</t>
+          <t>07/22 16:15:32</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/09 09:55:21</t>
+          <t>07/09 11:40:10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -781,12 +781,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/07 14:00:58</t>
+          <t>07/09 09:55:21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -808,83 +808,110 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>07/07 14:00:58</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>07/07 12:04:55</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>817000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>84893.05</t>
+          <t>817000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>71537</t>
+          <t>84893.05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>83511</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>13356.05</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1382.05</t>
         </is>
       </c>
     </row>
